--- a/Production/LatticeBoardV9/Lattice_Board_V9.xlsx
+++ b/Production/LatticeBoardV9/Lattice_Board_V9.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B56"/>
+  <dimension ref="A1:B58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="88" customWidth="1" min="1" max="1"/>
@@ -427,7 +427,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Lattice board V9.2 (24 x 14 in) - single-TA configuration + external-TA option</t>
+          <t>Lattice board V9.3 (24 x 14 in) - single-TA configuration + external-TA option</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>TA butterfly package (TAboard)</t>
+          <t>TA butterfly package (TAboard), mounted on the TA adapter</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -891,40 +891,54 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Counts come from the FreeCAD model (the *_validation.json audit report); adapters are per hana-branch Production/Adapters STEP names.</t>
+          <t>Which holes are tapped and which are not: see the *_TAP_or_NOT sheets next to the STEP file.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>The empty RSP05 mounts on the output rows receive a bonded PBS cube each (not modelled): add 1 cube per "empty rotating PBS RSP05".</t>
+          <t>Counts come from the FreeCAD model (the *_validation.json audit report); adapters are per hana-branch Production/Adapters STEP names.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>HKTS-5/64 adjusters are the two per M05 / KA05T mount (already included with the mounts if bought as kits).</t>
+          <t>The empty RSP05 mounts on the output rows receive a bonded PBS cube each (not modelled): add 1 cube per "empty rotating PBS RSP05".</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AOM seats are machined into the baseplate (integral seat, flat screw face); only the upper AOM adapter is a separate part.</t>
+          <t>HKTS-5/64 adjusters are the two per M05 / KA05T mount (already included with the mounts if bought as kits).</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Six common stations are drilled as bare 8-32 holes; no holder or optic is installed. They are sized for a POLARIS-L05G with a 10 mm cylindrical lens bonded to its front face (checked: &gt;= 2.31 mm to the nearest part at every station).</t>
+          <t>AOM seats are machined into the baseplate (integral seat, flat screw face); only the upper AOM adapter is a separate part.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
+        <is>
+          <t>V9.3: the TA butterfly board is screwed to the TA adapter (four M2.5 tapped in the adapter); the plate under the TA has only the adapter's four 8-32 taps, no M2.5 holes. Which holes are tapped: see the TAP_or_NOT sheets next to each STEP file.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Six common stations are drilled as bare 8-32 holes; no holder or optic is installed. They are sized for a POLARIS-L05G with a 10 mm cylindrical lens bonded to its front face (checked: &gt;= 2.31 mm to the nearest part at every station).</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
         <is>
           <t>The cell seat is a 104 x 56 x 19.05 mm pocket with four 8-32 corner taps. Nothing is installed there: the enclosure has not been designed yet, so no cell part is listed.</t>
         </is>

--- a/Production/LatticeBoardV9/Lattice_Board_V9.xlsx
+++ b/Production/LatticeBoardV9/Lattice_Board_V9.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B58"/>
+  <dimension ref="A1:B60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="88" customWidth="1" min="1" max="1"/>
@@ -427,7 +427,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Lattice board V9.3 (24 x 14 in) - single-TA configuration + external-TA option</t>
+          <t>Lattice board V9.4 (24 x 15 in, f = 300 folded cat-eyes) - single-TA configuration + external-TA option</t>
         </is>
       </c>
     </row>
@@ -517,7 +517,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Lattice_V9_2_baseplate_24x14in.step</t>
+          <t>Lattice_V9_4_baseplate_24x15in.step</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -554,7 +554,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16">
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21">
@@ -670,7 +670,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Lens LA1612-B</t>
+          <t>Lens LA1618-B</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="29">
@@ -891,14 +891,14 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Which holes are tapped and which are not: see the *_TAP_or_NOT sheets next to the STEP file.</t>
+          <t>Which holes are tapped and which are not: see Lattice_V9_4_baseplate_TAP_or_NOT next to the STEP file (102 x 8-32 tapped, 4 x 1/4-20 table-bolt clearance).</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Counts come from the FreeCAD model (the *_validation.json audit report); adapters are per hana-branch Production/Adapters STEP names.</t>
+          <t>Counts come from the FreeCAD model (Lattice_V9_dual_validation.json); adapters are per hana-branch Production/Adapters STEP names.</t>
         </is>
       </c>
     </row>
@@ -912,7 +912,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>HKTS-5/64 adjusters are the two per M05 / KA05T mount (already included with the mounts if bought as kits).</t>
+          <t>HKTS-5/64 adjusters are the two per M05 / KA05T mount (already included with the mounts if bought as kits). Every mirror on this board is in a Newport M05.</t>
         </is>
       </c>
     </row>
@@ -926,19 +926,33 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>V9.3: the TA butterfly board is screwed to the TA adapter (four M2.5 tapped in the adapter); the plate under the TA has only the adapter's four 8-32 taps, no M2.5 holes. Which holes are tapped: see the TAP_or_NOT sheets next to each STEP file.</t>
+          <t>Cat-eye lens LA1618-B (f = 300 mm, 1/2 in): catalogue R 155.0 / tc 2.2 / te 2.1 mm. The plate was laid out with R 154.5 / tc 2.0; the resulting 1.2 / 1.0 mm cat-eye defocus is accepted (see the script docstring).</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Six common stations are drilled as bare 8-32 holes; no holder or optic is installed. They are sized for a POLARIS-L05G with a 10 mm cylindrical lens bonded to its front face (checked: &gt;= 2.31 mm to the nearest part at every station).</t>
+          <t>The TA butterfly board is screwed to the TA adapter (four M2.5 tapped in the adapter); the plate under the TA has only the adapter's four 8-32 taps, no M2.5 holes. Which holes are tapped: see the TAP_or_NOT sheet next to the STEP file.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
+        <is>
+          <t>OPTIONAL f = 75 mm cat-eye (the V9.3 LA1612-B set), bare holes only, nothing installed and nothing listed above: per AOM arm one L05G tap, two RSP05 taps, one slide-mount tap and two M05 taps (lens-&gt;mirror 50 and 75). To use it: 1 x LA1612-B in a POLARIS-L05G, 1 x RSP05 + lip adapter with a 1/2 in QWP, 1 x IDA12 on the slide mount, 1 x M05 retro mirror per arm. The M05 at those positions has no thumbscrew pocket: drive its lower adjuster with a plain 5/64 hex key (no HKTS). The lens-&gt;mirror 75 mirror body stands where fold F1 (DP1) / F3 (DP2) is, so that fold comes off for a 75/75 test.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Six common stations are drilled as bare 8-32 holes; no holder or optic is installed. They are sized for a POLARIS-L05G with a 10 mm cylindrical lens bonded to its front face.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
         <is>
           <t>The cell seat is a 104 x 56 x 19.05 mm pocket with four 8-32 corner taps. Nothing is installed there: the enclosure has not been designed yet, so no cell part is listed.</t>
         </is>

--- a/Production/LatticeBoardV9/Lattice_Board_V9.xlsx
+++ b/Production/LatticeBoardV9/Lattice_Board_V9.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B60"/>
+  <dimension ref="A1:B61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="88" customWidth="1" min="1" max="1"/>
@@ -427,7 +427,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Lattice board V9.4 (24 x 15 in, f = 300 folded cat-eyes) - single-TA configuration + external-TA option</t>
+          <t>Lattice board V9.4.1 (24 x 15 in, f = 300 folded cat-eyes) - single-TA configuration + external-TA option</t>
         </is>
       </c>
     </row>
@@ -517,7 +517,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Lattice_V9_4_baseplate_24x15in.step</t>
+          <t>Lattice_V9_4_1_baseplate_24x15in.step</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -891,7 +891,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Which holes are tapped and which are not: see Lattice_V9_4_baseplate_TAP_or_NOT next to the STEP file (102 x 8-32 tapped, 4 x 1/4-20 table-bolt clearance).</t>
+          <t>Which holes are tapped and which are not: see Lattice_V9_4_1_baseplate_TAP_or_NOT next to the STEP file (102 x 8-32 tapped, 4 x 1/4-20 table-bolt clearance).</t>
         </is>
       </c>
     </row>
@@ -940,19 +940,26 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>OPTIONAL f = 75 mm cat-eye (the V9.3 LA1612-B set), bare holes only, nothing installed and nothing listed above: per AOM arm one L05G tap, two RSP05 taps, one slide-mount tap and two M05 taps (lens-&gt;mirror 50 and 75). To use it: 1 x LA1612-B in a POLARIS-L05G, 1 x RSP05 + lip adapter with a 1/2 in QWP, 1 x IDA12 on the slide mount, 1 x M05 retro mirror per arm. The M05 at those positions has no thumbscrew pocket: drive its lower adjuster with a plain 5/64 hex key (no HKTS). The lens-&gt;mirror 75 mirror body stands where fold F1 (DP1) / F3 (DP2) is, so that fold comes off for a 75/75 test.</t>
+          <t>Table bolts (V9.4.1): the four 1/4-20 clearance holes sit on the lab table 1 in grid with the plate fiber-side (right) edge 0.25 in inside the table edge - fiber-side pair 3.25 in from the right plate edge, 13 in apart, centred on the short edge; TA-side pair 19 in further left (1.5 in from the left edge), 11 in apart, centred. STEP coordinates (mm): (523.875, 12.7), (523.875, 342.9), (41.275, 38.1), (41.275, 317.5).</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Six common stations are drilled as bare 8-32 holes; no holder or optic is installed. They are sized for a POLARIS-L05G with a 10 mm cylindrical lens bonded to its front face.</t>
+          <t>OPTIONAL f = 75 mm cat-eye (the V9.3 LA1612-B set) on the 0-order (input) axis straight after each AOM, bare holes only, nothing installed and nothing listed above: per AOM arm one L05G tap, two RSP05 taps, one slide-mount tap and two M05 taps (lens-&gt;mirror 50 and 75). To use it: 1 x LA1612-B in a POLARIS-L05G, 1 x RSP05 + lip adapter with a 1/2 in QWP, 1 x IDA12 on the slide mount, 1 x M05 retro mirror per arm. The M05 at those positions has no thumbscrew pocket: drive its lower adjuster with a plain 5/64 hex key (no HKTS). The lens-&gt;mirror 75 mirror body stands where fold F1 (DP1) / F3 (DP2) is, so that fold comes off for a 75/75 test.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
+        <is>
+          <t>Six common stations are drilled as bare 8-32 holes; no holder or optic is installed. They are sized for a POLARIS-L05G with a 10 mm cylindrical lens bonded to its front face.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
         <is>
           <t>The cell seat is a 104 x 56 x 19.05 mm pocket with four 8-32 corner taps. Nothing is installed there: the enclosure has not been designed yet, so no cell part is listed.</t>
         </is>

--- a/Production/LatticeBoardV9/Lattice_Board_V9.xlsx
+++ b/Production/LatticeBoardV9/Lattice_Board_V9.xlsx
@@ -427,7 +427,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Lattice board V9.4.1 (24 x 15 in, f = 300 folded cat-eyes) - single-TA configuration + external-TA option</t>
+          <t>Lattice board V9.4.2 (24 x 15 in, f = 300 folded cat-eyes) - single-TA configuration + external-TA option</t>
         </is>
       </c>
     </row>
@@ -517,7 +517,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Lattice_V9_4_1_baseplate_24x15in.step</t>
+          <t>Lattice_V9_4_2_baseplate_24x15in.step</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -891,7 +891,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Which holes are tapped and which are not: see Lattice_V9_4_1_baseplate_TAP_or_NOT next to the STEP file (102 x 8-32 tapped, 4 x 1/4-20 table-bolt clearance).</t>
+          <t>Which holes are tapped and which are not: see Lattice_V9_4_2_baseplate_TAP_or_NOT next to the STEP file (102 x 8-32 tapped, 4 x 1/4-20 table-bolt clearance).</t>
         </is>
       </c>
     </row>
@@ -940,7 +940,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Table bolts (V9.4.1): the four 1/4-20 clearance holes sit on the lab table 1 in grid with the plate fiber-side (right) edge 0.25 in inside the table edge - fiber-side pair 3.25 in from the right plate edge, 13 in apart, centred on the short edge; TA-side pair 19 in further left (1.5 in from the left edge), 11 in apart, centred. STEP coordinates (mm): (523.875, 12.7), (523.875, 342.9), (41.275, 38.1), (41.275, 317.5).</t>
+          <t>Table bolts (V9.4.2): the four 1/4-20 clearance holes sit on the lab table 1 in grid with the plate fiber-side (right) edge 0.25 in inside the table edge; both pairs 10 in apart and centred on the short edge - fiber-side pair 6.25 in from the right plate edge, TA-side pair 1.5 in from the left edge (16 in further left). STEP coordinates (mm): (447.675, 50.8), (447.675, 304.8), (41.275, 50.8), (41.275, 304.8).</t>
         </is>
       </c>
     </row>

--- a/Production/LatticeBoardV9/Lattice_Board_V9.xlsx
+++ b/Production/LatticeBoardV9/Lattice_Board_V9.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B61"/>
+  <dimension ref="A1:B66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="88" customWidth="1" min="1" max="1"/>
@@ -427,7 +427,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Lattice board V9.4.2 (24 x 15 in, f = 300 folded cat-eyes) - single-TA configuration + external-TA option</t>
+          <t>Lattice board V9.5 (24 x 15 in, f = 300 folded cat-eyes, sliding Rb cell enclosure) - single-TA configuration + external-TA option</t>
         </is>
       </c>
     </row>
@@ -477,7 +477,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Shutter_Adapter.step</t>
+          <t>Rb_Cell_Enclosure_Body_V9_5.step (Production/CellEnclosure; machined, 76 x 40.4 x 48 with the slot shoulder)</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -487,27 +487,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Surface_Adapter_isolator_lip.step</t>
+          <t>Rb_Cell_Enclosure_Cover_V9_5.step (Production/CellEnclosure; machined, 10 mm end cover, no aperture yet)</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Surface_Adapter_rsp05_lip.step</t>
+          <t>Shutter_Adapter.step</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TA_adapter.step</t>
+          <t>Surface_Adapter_isolator_lip.step</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -517,100 +517,100 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Lattice_V9_4_2_baseplate_24x15in.step</t>
+          <t>Surface_Adapter_rsp05_lip.step</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TA_adapter.step</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+    </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>Elements</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>8-32 UNC x 3/4 in socket head cap screw (8 cover screws + 2 slot screws of the cell enclosure)</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1/2 in half-wave waveplate (HWP)</t>
+          <t>#8 flat washer (under the two slot screws)</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1/2 in mirror (BB05-E03 or equivalent)</t>
+          <t>Lattice_V9_5_baseplate_24x15in.step</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>1/2 in quarter-wave waveplate (QWP)</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>3</v>
-      </c>
-    </row>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16"/>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>1/4-20 table bolt (baseplate fixing)</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>4</v>
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>Elements</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C220TMD-A fiber lens</t>
+          <t>1/2 in half-wave waveplate (HWP)</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>G&amp;H AOMO 3100-125</t>
+          <t>1/2 in mirror (BB05-E03 or equivalent)</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>HKTS-5/64 thumbscrew adjuster</t>
+          <t>1/2 in quarter-wave waveplate (QWP)</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>IDA12-P5 iris</t>
+          <t>1/4-20 table bolt (baseplate fixing)</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -620,17 +620,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>IOT-5-850-VLP isolator (113.5 mm plate pocket)</t>
+          <t>C220TMD-A fiber lens</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>KA05T fiber port mount (rear tail-clamp hole pair drilled in the plate: lattice 76 mm, TA / AOM boards 82.7 mm behind the head)</t>
+          <t>G&amp;H AOMO 3100-125</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -640,37 +640,37 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>KM100PM (bridged)</t>
+          <t>HKTS-5/64 thumbscrew adjuster</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Lens LA1289-B</t>
+          <t>IDA12-P5 iris</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Lens LA1540-B</t>
+          <t>IOT-5-850-VLP isolator (113.5 mm plate pocket)</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Lens LA1618-B</t>
+          <t>KA05T fiber port mount (rear tail-clamp hole pair drilled in the plate: lattice 76 mm, TA / AOM boards 82.7 mm behind the head)</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -680,120 +680,127 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Newport M05 mirror mount</t>
+          <t>KM100PM (bridged)</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PBS cube 12.7 mm</t>
+          <t>Lens LA1289-B</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>POLARIS-L05G lens holder (no alignment-pin slots cut)</t>
+          <t>Lens LA1540-B</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>RSP05 rotation mount</t>
+          <t>Lens LA1618-B</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>S05TM09</t>
+          <t>Newport M05 mirror mount</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SM05FCA2</t>
+          <t>PBS cube 12.7 mm</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SM05L05</t>
+          <t>POLARIS-L05G lens holder (no alignment-pin slots cut)</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SRS SR475 shutter</t>
+          <t>RSP05 rotation mount</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>TA butterfly package (TAboard), mounted on the TA adapter</t>
+          <t>Rb vapour cell GC25075-RB (25.4 x 71.84 mm, fill stem up)</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="37"/>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>S05TM09</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>2</v>
+      </c>
+    </row>
     <row r="38">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>External-TA option only (not installed in the single-TA configuration)</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>SM05FCA2</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Iris_Mount.step (IDA12 slide mount)</t>
+          <t>SM05L05</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1/2 in mirror (BB05-E03 or equivalent)</t>
+          <t>SRS SR475 shutter</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -803,37 +810,30 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>C220TMD-A fiber lens</t>
+          <t>TA butterfly package (TAboard), mounted on the TA adapter</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>HKTS-5/64 thumbscrew adjuster</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>4</v>
-      </c>
-    </row>
+    <row r="42"/>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>IDA12-P5 iris</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>1</v>
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>External-TA option only (not installed in the single-TA configuration)</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>KA05T fiber port mount (rear tail-clamp hole pair drilled in the plate: lattice 76 mm, TA / AOM boards 82.7 mm behind the head)</t>
+          <t>Iris_Mount.step (IDA12 slide mount)</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -843,7 +843,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Newport M05 mirror mount</t>
+          <t>1/2 in mirror (BB05-E03 or equivalent)</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -853,7 +853,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>S05TM09</t>
+          <t>C220TMD-A fiber lens</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -863,105 +863,155 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SM05FCA2</t>
+          <t>HKTS-5/64 thumbscrew adjuster</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SM05L05</t>
+          <t>IDA12-P5 iris</t>
         </is>
       </c>
       <c r="B48" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="49"/>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>KA05T fiber port mount (rear tail-clamp hole pair drilled in the plate: lattice 76 mm, TA / AOM boards 82.7 mm behind the head)</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1</v>
+      </c>
+    </row>
     <row r="50">
-      <c r="A50" s="1" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Newport M05 mirror mount</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Which holes are tapped and which are not: see Lattice_V9_4_2_baseplate_TAP_or_NOT next to the STEP file (102 x 8-32 tapped, 4 x 1/4-20 table-bolt clearance).</t>
-        </is>
+          <t>S05TM09</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Counts come from the FreeCAD model (Lattice_V9_dual_validation.json); adapters are per hana-branch Production/Adapters STEP names.</t>
-        </is>
+          <t>SM05FCA2</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>The empty RSP05 mounts on the output rows receive a bonded PBS cube each (not modelled): add 1 cube per "empty rotating PBS RSP05".</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>HKTS-5/64 adjusters are the two per M05 / KA05T mount (already included with the mounts if bought as kits). Every mirror on this board is in a Newport M05.</t>
-        </is>
-      </c>
-    </row>
+          <t>SM05L05</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54"/>
     <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>AOM seats are machined into the baseplate (integral seat, flat screw face); only the upper AOM adapter is a separate part.</t>
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Cat-eye lens LA1618-B (f = 300 mm, 1/2 in): catalogue R 155.0 / tc 2.2 / te 2.1 mm. The plate was laid out with R 154.5 / tc 2.0; the resulting 1.2 / 1.0 mm cat-eye defocus is accepted (see the script docstring).</t>
+          <t>Which holes are tapped and which are not: see Lattice_V9_5_baseplate_TAP_or_NOT next to the STEP file (100 x 8-32 tapped, 4 x 1/4-20 table-bolt clearance).</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>The TA butterfly board is screwed to the TA adapter (four M2.5 tapped in the adapter); the plate under the TA has only the adapter's four 8-32 taps, no M2.5 holes. Which holes are tapped: see the TAP_or_NOT sheet next to the STEP file.</t>
+          <t>Counts come from the FreeCAD model (Lattice_V9_dual_validation.json); adapters are per hana-branch Production/Adapters STEP names.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Table bolts (V9.4.2): the four 1/4-20 clearance holes sit on the lab table 1 in grid with the plate fiber-side (right) edge 0.25 in inside the table edge; both pairs 10 in apart and centred on the short edge - fiber-side pair 6.25 in from the right plate edge, TA-side pair 1.5 in from the left edge (16 in further left). STEP coordinates (mm): (447.675, 50.8), (447.675, 304.8), (41.275, 50.8), (41.275, 304.8).</t>
+          <t>The empty RSP05 mounts on the output rows receive a bonded PBS cube each (not modelled): add 1 cube per "empty rotating PBS RSP05".</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>OPTIONAL f = 75 mm cat-eye (the V9.3 LA1612-B set) on the 0-order (input) axis straight after each AOM, bare holes only, nothing installed and nothing listed above: per AOM arm one L05G tap, two RSP05 taps, one slide-mount tap and two M05 taps (lens-&gt;mirror 50 and 75). To use it: 1 x LA1612-B in a POLARIS-L05G, 1 x RSP05 + lip adapter with a 1/2 in QWP, 1 x IDA12 on the slide mount, 1 x M05 retro mirror per arm. The M05 at those positions has no thumbscrew pocket: drive its lower adjuster with a plain 5/64 hex key (no HKTS). The lens-&gt;mirror 75 mirror body stands where fold F1 (DP1) / F3 (DP2) is, so that fold comes off for a 75/75 test.</t>
+          <t>HKTS-5/64 adjusters are the two per M05 / KA05T mount (already included with the mounts if bought as kits). Every mirror on this board is in a Newport M05.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Six common stations are drilled as bare 8-32 holes; no holder or optic is installed. They are sized for a POLARIS-L05G with a 10 mm cylindrical lens bonded to its front face.</t>
+          <t>AOM seats are machined into the baseplate (integral seat, flat screw face); only the upper AOM adapter is a separate part.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>The cell seat is a 104 x 56 x 19.05 mm pocket with four 8-32 corner taps. Nothing is installed there: the enclosure has not been designed yet, so no cell part is listed.</t>
+          <t>Cat-eye lens LA1618-B (f = 300 mm, 1/2 in): catalogue R 155.0 / tc 2.2 / te 2.1 mm. The plate was laid out with R 154.5 / tc 2.0; the resulting 1.2 / 1.0 mm cat-eye defocus is accepted (see the script docstring).</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>The TA butterfly board is screwed to the TA adapter (four M2.5 tapped in the adapter); the plate under the TA has only the adapter's four 8-32 taps, no M2.5 holes. Which holes are tapped: see the TAP_or_NOT sheet next to the STEP file.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Table bolts (V9.4.2): the four 1/4-20 clearance holes sit on the lab table 1 in grid with the plate fiber-side (right) edge 0.25 in inside the table edge; both pairs 10 in apart and centred on the short edge - fiber-side pair 6.25 in from the right plate edge, TA-side pair 1.5 in from the left edge (16 in further left). STEP coordinates (mm): (447.675, 50.8), (447.675, 304.8), (41.275, 50.8), (41.275, 304.8).</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>OPTIONAL f = 75 mm cat-eye (the V9.3 LA1612-B set) on the 0-order (input) axis straight after each AOM, bare holes only, nothing installed and nothing listed above: per AOM arm one L05G tap, two RSP05 taps, one slide-mount tap and two M05 taps (lens-&gt;mirror 50 and 75). To use it: 1 x LA1612-B in a POLARIS-L05G, 1 x RSP05 + lip adapter with a 1/2 in QWP, 1 x IDA12 on the slide mount, 1 x M05 retro mirror per arm. The M05 at those positions has no thumbscrew pocket: drive its lower adjuster with a plain 5/64 hex key (no HKTS). The lens-&gt;mirror 75 mirror body stands where fold F1 (DP1) / F3 (DP2) is, so that fold comes off for a 75/75 test.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Six common stations are drilled as bare 8-32 holes; no holder or optic is installed. They are sized for a POLARIS-L05G with a 10 mm cylindrical lens bonded to its front face.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>V9.5 cell seat: a 10.3 mm deep pocket (100 x 61.4 mm plus a 48 x 27 mm ear) with two 8-32 taps through its floor at (223.35, 132) and (223.35, 162). The sliding enclosure (body + 2 end covers, Production/CellEnclosure) sits in it on two 8-32 x 3/4 in screws with #8 washers through the slots of its shoulder; travel 12.7 mm toward -x (beam through the cell centre .. along the cell wall). The covers are held by 8 x 8-32 x 3/4 in socket head cap screws (counterbored, 16 mm deep taps in the body). Beam apertures in the covers are not yet machined.</t>
         </is>
       </c>
     </row>

--- a/Production/LatticeBoardV9/Lattice_Board_V9.xlsx
+++ b/Production/LatticeBoardV9/Lattice_Board_V9.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B66"/>
+  <dimension ref="A1:B67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="88" customWidth="1" min="1" max="1"/>
@@ -427,7 +427,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Lattice board V9.5 (24 x 15 in, f = 300 folded cat-eyes, sliding Rb cell enclosure) - single-TA configuration + external-TA option</t>
+          <t>Lattice board V9.6 (24 x 15 in, f = 300 folded cat-eyes, split plain-block sliding Rb cell enclosure) - single-TA configuration + external-TA option</t>
         </is>
       </c>
     </row>
@@ -477,27 +477,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Rb_Cell_Enclosure_Body_V9_5.step (Production/CellEnclosure; machined, 76 x 40.4 x 48 with the slot shoulder)</t>
+          <t>Rb_Cell_Enclosure_Cover_V9_6.step (Production/CellEnclosure; machined, 8 mm end cover, no aperture yet)</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Rb_Cell_Enclosure_Cover_V9_5.step (Production/CellEnclosure; machined, 10 mm end cover, no aperture yet)</t>
+          <t>Rb_Cell_Enclosure_Lid_V9_6.step (Production/CellEnclosure; machined upper half 82 x 43.9 x 24, through slot + counter-slot)</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Shutter_Adapter.step</t>
+          <t>Rb_Cell_Enclosure_LowerHalf_V9_6.step (Production/CellEnclosure; machined plain block 82 x 43.9 x 24, through slot)</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -507,7 +507,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Surface_Adapter_isolator_lip.step</t>
+          <t>Shutter_Adapter.step</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -517,120 +517,120 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Surface_Adapter_rsp05_lip.step</t>
+          <t>Surface_Adapter_isolator_lip.step</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TA_adapter.step</t>
+          <t>Surface_Adapter_rsp05_lip.step</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>8-32 UNC x 3/4 in socket head cap screw (8 cover screws + 2 slot screws of the cell enclosure)</t>
+          <t>TA_adapter.step</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>#8 flat washer (under the two slot screws)</t>
+          <t>8-32 UNC x 5/8 in socket head cap screw (8 cover screws of the cell enclosure)</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Lattice_V9_5_baseplate_24x15in.step</t>
+          <t>8-32 UNC x 2 in socket head cap screw (through the enclosure slot into the plate)</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Lattice_V9_6_baseplate_24x15in.step</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
         <is>
           <t>Elements</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>#</t>
         </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>1/2 in half-wave waveplate (HWP)</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1/2 in mirror (BB05-E03 or equivalent)</t>
+          <t>1/2 in half-wave waveplate (HWP)</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1/2 in quarter-wave waveplate (QWP)</t>
+          <t>1/2 in mirror (BB05-E03 or equivalent)</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1/4-20 table bolt (baseplate fixing)</t>
+          <t>1/2 in quarter-wave waveplate (QWP)</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C220TMD-A fiber lens</t>
+          <t>1/4-20 table bolt (baseplate fixing)</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>G&amp;H AOMO 3100-125</t>
+          <t>C220TMD-A fiber lens</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -640,47 +640,47 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>HKTS-5/64 thumbscrew adjuster</t>
+          <t>G&amp;H AOMO 3100-125</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>36</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>IDA12-P5 iris</t>
+          <t>HKTS-5/64 thumbscrew adjuster</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4</v>
+        <v>36</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>IOT-5-850-VLP isolator (113.5 mm plate pocket)</t>
+          <t>IDA12-P5 iris</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>KA05T fiber port mount (rear tail-clamp hole pair drilled in the plate: lattice 76 mm, TA / AOM boards 82.7 mm behind the head)</t>
+          <t>IOT-5-850-VLP isolator (113.5 mm plate pocket)</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>KM100PM (bridged)</t>
+          <t>KA05T fiber port mount (rear tail-clamp hole pair drilled in the plate: lattice 76 mm, TA / AOM boards 82.7 mm behind the head)</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -690,7 +690,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Lens LA1289-B</t>
+          <t>KM100PM (bridged)</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -700,7 +700,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Lens LA1540-B</t>
+          <t>Lens LA1289-B</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -710,7 +710,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lens LA1618-B</t>
+          <t>Lens LA1540-B</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -720,67 +720,67 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Newport M05 mirror mount</t>
+          <t>Lens LA1618-B</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>PBS cube 12.7 mm</t>
+          <t>Newport M05 mirror mount</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>POLARIS-L05G lens holder (no alignment-pin slots cut)</t>
+          <t>PBS cube 12.7 mm</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>RSP05 rotation mount</t>
+          <t>POLARIS-L05G lens holder (no alignment-pin slots cut)</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rb vapour cell GC25075-RB (25.4 x 71.84 mm, fill stem up)</t>
+          <t>RSP05 rotation mount</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>S05TM09</t>
+          <t>Rb vapour cell GC25075-RB (25.4 x 71.84 mm, fill stem sideways in the parting plane, toward board -x)</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SM05FCA2</t>
+          <t>S05TM09</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -790,7 +790,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SM05L05</t>
+          <t>SM05FCA2</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -800,50 +800,50 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SRS SR475 shutter</t>
+          <t>SM05L05</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>SRS SR475 shutter</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>TA butterfly package (TAboard), mounted on the TA adapter</t>
         </is>
       </c>
-      <c r="B41" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42"/>
-    <row r="43">
-      <c r="A43" s="1" t="inlineStr">
+      <c r="B42" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43"/>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
         <is>
           <t>External-TA option only (not installed in the single-TA configuration)</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>#</t>
         </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Iris_Mount.step (IDA12 slide mount)</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1/2 in mirror (BB05-E03 or equivalent)</t>
+          <t>Iris_Mount.step (IDA12 slide mount)</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -853,7 +853,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>C220TMD-A fiber lens</t>
+          <t>1/2 in mirror (BB05-E03 or equivalent)</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -863,27 +863,27 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>HKTS-5/64 thumbscrew adjuster</t>
+          <t>C220TMD-A fiber lens</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>IDA12-P5 iris</t>
+          <t>HKTS-5/64 thumbscrew adjuster</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>KA05T fiber port mount (rear tail-clamp hole pair drilled in the plate: lattice 76 mm, TA / AOM boards 82.7 mm behind the head)</t>
+          <t>IDA12-P5 iris</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -893,7 +893,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Newport M05 mirror mount</t>
+          <t>KA05T fiber port mount (rear tail-clamp hole pair drilled in the plate: lattice 76 mm, TA / AOM boards 82.7 mm behind the head)</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -903,7 +903,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>S05TM09</t>
+          <t>Newport M05 mirror mount</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -913,7 +913,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SM05FCA2</t>
+          <t>S05TM09</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -923,95 +923,105 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>SM05FCA2</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
           <t>SM05L05</t>
         </is>
       </c>
-      <c r="B53" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54"/>
-    <row r="55">
-      <c r="A55" s="1" t="inlineStr">
+      <c r="B54" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55"/>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Which holes are tapped and which are not: see Lattice_V9_5_baseplate_TAP_or_NOT next to the STEP file (100 x 8-32 tapped, 4 x 1/4-20 table-bolt clearance).</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Counts come from the FreeCAD model (Lattice_V9_dual_validation.json); adapters are per hana-branch Production/Adapters STEP names.</t>
+          <t>Which holes are tapped and which are not: see Lattice_V9_6_baseplate_TAP_or_NOT next to the STEP file (99 x 8-32 tapped, 4 x 1/4-20 table-bolt clearance).</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>The empty RSP05 mounts on the output rows receive a bonded PBS cube each (not modelled): add 1 cube per "empty rotating PBS RSP05".</t>
+          <t>Counts come from the FreeCAD model (Lattice_V9_dual_validation.json); adapters are per hana-branch Production/Adapters STEP names.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>HKTS-5/64 adjusters are the two per M05 / KA05T mount (already included with the mounts if bought as kits). Every mirror on this board is in a Newport M05.</t>
+          <t>The empty RSP05 mounts on the output rows receive a bonded PBS cube each (not modelled): add 1 cube per "empty rotating PBS RSP05".</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AOM seats are machined into the baseplate (integral seat, flat screw face); only the upper AOM adapter is a separate part.</t>
+          <t>HKTS-5/64 adjusters are the two per M05 / KA05T mount (already included with the mounts if bought as kits). Every mirror on this board is in a Newport M05.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Cat-eye lens LA1618-B (f = 300 mm, 1/2 in): catalogue R 155.0 / tc 2.2 / te 2.1 mm. The plate was laid out with R 154.5 / tc 2.0; the resulting 1.2 / 1.0 mm cat-eye defocus is accepted (see the script docstring).</t>
+          <t>AOM seats are machined into the baseplate (integral seat, flat screw face); only the upper AOM adapter is a separate part.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>The TA butterfly board is screwed to the TA adapter (four M2.5 tapped in the adapter); the plate under the TA has only the adapter's four 8-32 taps, no M2.5 holes. Which holes are tapped: see the TAP_or_NOT sheet next to the STEP file.</t>
+          <t>Cat-eye lens LA1618-B (f = 300 mm, 1/2 in): catalogue R 155.0 / tc 2.2 / te 2.1 mm. The plate was laid out with R 154.5 / tc 2.0; the resulting 1.2 / 1.0 mm cat-eye defocus is accepted (see the script docstring).</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Table bolts (V9.4.2): the four 1/4-20 clearance holes sit on the lab table 1 in grid with the plate fiber-side (right) edge 0.25 in inside the table edge; both pairs 10 in apart and centred on the short edge - fiber-side pair 6.25 in from the right plate edge, TA-side pair 1.5 in from the left edge (16 in further left). STEP coordinates (mm): (447.675, 50.8), (447.675, 304.8), (41.275, 50.8), (41.275, 304.8).</t>
+          <t>The TA butterfly board is screwed to the TA adapter (four M2.5 tapped in the adapter); the plate under the TA has only the adapter's four 8-32 taps, no M2.5 holes. Which holes are tapped: see the TAP_or_NOT sheet next to the STEP file.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>OPTIONAL f = 75 mm cat-eye (the V9.3 LA1612-B set) on the 0-order (input) axis straight after each AOM, bare holes only, nothing installed and nothing listed above: per AOM arm one L05G tap, two RSP05 taps, one slide-mount tap and two M05 taps (lens-&gt;mirror 50 and 75). To use it: 1 x LA1612-B in a POLARIS-L05G, 1 x RSP05 + lip adapter with a 1/2 in QWP, 1 x IDA12 on the slide mount, 1 x M05 retro mirror per arm. The M05 at those positions has no thumbscrew pocket: drive its lower adjuster with a plain 5/64 hex key (no HKTS). The lens-&gt;mirror 75 mirror body stands where fold F1 (DP1) / F3 (DP2) is, so that fold comes off for a 75/75 test.</t>
+          <t>Table bolts (V9.4.2): the four 1/4-20 clearance holes sit on the lab table 1 in grid with the plate fiber-side (right) edge 0.25 in inside the table edge; both pairs 10 in apart and centred on the short edge - fiber-side pair 6.25 in from the right plate edge, TA-side pair 1.5 in from the left edge (16 in further left). STEP coordinates (mm): (447.675, 50.8), (447.675, 304.8), (41.275, 50.8), (41.275, 304.8).</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Six common stations are drilled as bare 8-32 holes; no holder or optic is installed. They are sized for a POLARIS-L05G with a 10 mm cylindrical lens bonded to its front face.</t>
+          <t>OPTIONAL f = 75 mm cat-eye (the V9.3 LA1612-B set) on the 0-order (input) axis straight after each AOM, bare holes only, nothing installed and nothing listed above: per AOM arm one L05G tap, two RSP05 taps, one slide-mount tap and two M05 taps (lens-&gt;mirror 50 and 75). To use it: 1 x LA1612-B in a POLARIS-L05G, 1 x RSP05 + lip adapter with a 1/2 in QWP, 1 x IDA12 on the slide mount, 1 x M05 retro mirror per arm. The M05 at those positions has no thumbscrew pocket: drive its lower adjuster with a plain 5/64 hex key (no HKTS). The lens-&gt;mirror 75 mirror body stands where fold F1 (DP1) / F3 (DP2) is, so that fold comes off for a 75/75 test.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>V9.5 cell seat: a 10.3 mm deep pocket (100 x 61.4 mm plus a 48 x 27 mm ear) with two 8-32 taps through its floor at (223.35, 132) and (223.35, 162). The sliding enclosure (body + 2 end covers, Production/CellEnclosure) sits in it on two 8-32 x 3/4 in screws with #8 washers through the slots of its shoulder; travel 12.7 mm toward -x (beam through the cell centre .. along the cell wall). The covers are held by 8 x 8-32 x 3/4 in socket head cap screws (counterbored, 16 mm deep taps in the body). Beam apertures in the covers are not yet machined.</t>
+          <t>Six common stations are drilled as bare 8-32 holes; no holder or optic is installed. They are sized for a POLARIS-L05G with a 10 mm cylindrical lens bonded to its front face.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>V9.6 cell seat: an 11.3 mm deep pocket (102 x 61.7 mm, board x 160.8..222.5 / y 114..216) with one 8-32 tap through its floor at (185, 201.3). The split plain-block enclosure (lower half + lid + 2 end covers, Production/CellEnclosure) sits in it; one 8-32 x 2 in screw goes from the lid top through the slot of both halves (in the bore end region beyond the cell) into the tap and clamps the halves and the position; travel 10.5 mm toward -x (beam through the cell centre .. 2.2 mm inside the cell wall). The end covers (8 mm) are held by 8 x 8-32 x 5/8 in socket head cap screws (counterbored, 16 mm deep taps, two in each half) and tie the halves together. The fill stem lies in the parting plane toward -x in a 12 x 10 channel; a 6 x 6 cable notch leaves the lower half on the same side. Beam apertures in the covers are not yet machined.</t>
         </is>
       </c>
     </row>

--- a/Production/LatticeBoardV9/Lattice_Board_V9.xlsx
+++ b/Production/LatticeBoardV9/Lattice_Board_V9.xlsx
@@ -427,7 +427,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Lattice board V9.6 (24 x 15 in, f = 300 folded cat-eyes, split plain-block sliding Rb cell enclosure) - single-TA configuration + external-TA option</t>
+          <t>Lattice board V9.7 (24 x 15 in, f = 300 folded cat-eyes, split plain-block sliding Rb cell enclosure, two end screws) - single-TA configuration + external-TA option</t>
         </is>
       </c>
     </row>
@@ -477,7 +477,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Rb_Cell_Enclosure_Cover_V9_6.step (Production/CellEnclosure; machined, 8 mm end cover, no aperture yet)</t>
+          <t>Rb_Cell_Enclosure_Cover_V9_7.step (Production/CellEnclosure; machined, 7 mm end cover, no aperture yet)</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -487,7 +487,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Rb_Cell_Enclosure_Lid_V9_6.step (Production/CellEnclosure; machined upper half 82 x 43.9 x 24, through slot + counter-slot)</t>
+          <t>Rb_Cell_Enclosure_Lid_V9_7.step (Production/CellEnclosure; machined upper half 88 x 46.9 x 24, two through slots + counter-slots)</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -497,7 +497,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Rb_Cell_Enclosure_LowerHalf_V9_6.step (Production/CellEnclosure; machined plain block 82 x 43.9 x 24, through slot)</t>
+          <t>Rb_Cell_Enclosure_LowerHalf_V9_7.step (Production/CellEnclosure; machined plain block 88 x 46.9 x 24, two through slots, closed stem pocket)</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -557,17 +557,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>8-32 UNC x 2 in socket head cap screw (through the enclosure slot into the plate)</t>
+          <t>8-32 UNC x 2 in socket head cap screw (through the enclosure slots into the plate, one per end)</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Lattice_V9_6_baseplate_24x15in.step</t>
+          <t>Lattice_V9_7_baseplate_24x15in.step</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -951,7 +951,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Which holes are tapped and which are not: see Lattice_V9_6_baseplate_TAP_or_NOT next to the STEP file (99 x 8-32 tapped, 4 x 1/4-20 table-bolt clearance).</t>
+          <t>Which holes are tapped and which are not: see Lattice_V9_7_baseplate_TAP_or_NOT next to the STEP file (100 x 8-32 tapped, 4 x 1/4-20 table-bolt clearance).</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>V9.6 cell seat: an 11.3 mm deep pocket (102 x 61.7 mm, board x 160.8..222.5 / y 114..216) with one 8-32 tap through its floor at (185, 201.3). The split plain-block enclosure (lower half + lid + 2 end covers, Production/CellEnclosure) sits in it; one 8-32 x 2 in screw goes from the lid top through the slot of both halves (in the bore end region beyond the cell) into the tap and clamps the halves and the position; travel 10.5 mm toward -x (beam through the cell centre .. 2.2 mm inside the cell wall). The end covers (8 mm) are held by 8 x 8-32 x 5/8 in socket head cap screws (counterbored, 16 mm deep taps, two in each half) and tie the halves together. The fill stem lies in the parting plane toward -x in a 12 x 10 channel; a 6 x 6 cable notch leaves the lower half on the same side. Beam apertures in the covers are not yet machined.</t>
+          <t>V9.7 cell seat: an 11.3 mm deep pocket (104.4 x 64.7 mm, board x 157.8..222.5 / y 111.3..215.7) with two 8-32 taps through its floor at (185, 123.6) and (185, 203.4). The split plain-block enclosure (lower half + lid + 2 end covers, Production/CellEnclosure) sits in it; two 8-32 x 2 in screws, one per end, go from the lid top through the slots of both halves (in the bore end regions beyond the cell) into the taps and clamp the halves and the position; travel 10.5 mm toward -x (beam through the cell centre .. 2.2 mm inside the cell wall). The end covers (7 mm) are held by 8 x 8-32 x 5/8 in socket head cap screws (counterbored 3.5, 16 mm deep taps, two in each half) and tie the halves together. The fill stem (Thorlabs 24088-E0W: mid-length, &lt; 10 mm high) lies in the parting plane toward -x in a closed 12 x 10 pocket; a 6 x 6 cable notch leaves the lower half on the same side. Beam apertures in the covers are not yet machined.</t>
         </is>
       </c>
     </row>

--- a/Production/LatticeBoardV9/Lattice_Board_V9.xlsx
+++ b/Production/LatticeBoardV9/Lattice_Board_V9.xlsx
@@ -427,7 +427,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Lattice board V9.7 (24 x 15 in, f = 300 folded cat-eyes, split plain-block sliding Rb cell enclosure, two end screws) - single-TA configuration + external-TA option</t>
+          <t>Lattice board V9.7 with cell enclosure V9.16 (24 x 15 in, f = 300 folded cat-eyes, sliding Rb cell enclosure of two identical half bodies, two end screws) - single-TA configuration + external-TA option</t>
         </is>
       </c>
     </row>
@@ -477,7 +477,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Rb_Cell_Enclosure_Cover_V9_7.step (Production/CellEnclosure; machined, 7 mm end cover, no aperture yet)</t>
+          <t>Rb_Cell_Enclosure_Cover_V9_16.step (Production/CellEnclosure; machined, 7 mm end cover, no aperture yet)</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -487,17 +487,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Rb_Cell_Enclosure_Lid_V9_7.step (Production/CellEnclosure; machined upper half 88 x 46.9 x 24, two through slots + counter-slots)</t>
+          <t>Rb_Cell_Enclosure_HalfBody_V9_16.step (Production/CellEnclosure; machined half body 88 x 46.9 x 24, two plain through slots; lower and upper half are this same part)</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Rb_Cell_Enclosure_LowerHalf_V9_7.step (Production/CellEnclosure; machined plain block 88 x 46.9 x 24, two through slots, closed stem pocket)</t>
+          <t>Shutter_Adapter.step</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -507,7 +507,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Shutter_Adapter.step</t>
+          <t>Surface_Adapter_isolator_lip.step</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -517,47 +517,47 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Surface_Adapter_isolator_lip.step</t>
+          <t>Surface_Adapter_rsp05_lip.step</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Surface_Adapter_rsp05_lip.step</t>
+          <t>TA_adapter.step</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TA_adapter.step</t>
+          <t>8-32 UNC x 5/8 in socket head cap screw (8 cover screws of the cell enclosure)</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>8-32 UNC x 5/8 in socket head cap screw (8 cover screws of the cell enclosure)</t>
+          <t>8-32 UNC x 2-1/4 in socket head cap screw (through the slots of both enclosure halves into the plate, one per end)</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>8-32 UNC x 2 in socket head cap screw (through the enclosure slots into the plate, one per end)</t>
+          <t>#8 flat washer (under the two 2-1/4 in screw heads, on the slots)</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -951,7 +951,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Which holes are tapped and which are not: see Lattice_V9_7_baseplate_TAP_or_NOT next to the STEP file (100 x 8-32 tapped, 4 x 1/4-20 table-bolt clearance).</t>
+          <t>Which holes are tapped and which are not: see Lattice_V9_7_baseplate_TAP_or_NOT next to the STEP file (100 x 8-32 tapped, 4 x 1/4-20 table-bolt clearance); for the cell enclosure parts see Production/CellEnclosure/Rb_Cell_Enclosure_V9_16_3D_TAP.png.</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>V9.7 cell seat: an 11.3 mm deep pocket (104.4 x 64.7 mm, board x 157.8..222.5 / y 111.3..215.7) with two 8-32 taps through its floor at (185, 123.6) and (185, 203.4). The split plain-block enclosure (lower half + lid + 2 end covers, Production/CellEnclosure) sits in it; two 8-32 x 2 in screws, one per end, go from the lid top through the slots of both halves (in the bore end regions beyond the cell) into the taps and clamp the halves and the position; travel 10.5 mm toward -x (beam through the cell centre .. 2.2 mm inside the cell wall). The end covers (7 mm) are held by 8 x 8-32 x 5/8 in socket head cap screws (counterbored 3.5, 16 mm deep taps, two in each half) and tie the halves together. The fill stem (Thorlabs 24088-E0W: mid-length, &lt; 10 mm high) lies in the parting plane toward -x in a closed 12 x 10 pocket; a 6 x 6 cable notch leaves the lower half on the same side. Beam apertures in the covers are not yet machined.</t>
+          <t>Cell enclosure V9.16 (the plate and its seat are unchanged since V9.7): the seat is an 11.3 mm deep pocket (104.4 x 64.7 mm, board x 157.8..222.5 / y 111.3..215.7) with two 8-32 taps through its floor at (185, 123.6) and (185, 203.4). The split plain-block enclosure is 2 identical half bodies (the upper one is the lower one turned over) + 2 identical end covers (Production/CellEnclosure). Two 8-32 x 2-1/4 in socket head cap screws with #8 flat washers, one per end, go from the top face through the plain through slots of both halves (in the bore end regions beyond the cell; no counter-slot, the heads sit on the top face) into the taps (9.2 mm of thread in the 14.1 mm pocket floor) and clamp the halves and the position; travel 10.5 mm toward -x (beam through the cell centre .. 2.2 mm inside the cell wall). The end covers (7 mm) are held by 8 x 8-32 x 5/8 in socket head cap screws (counterbored 3.5, 16 mm deep taps, two in each end face of each half) and tie the halves together. The fill stem (Thorlabs 24088-E0W: mid-length, &lt; 10 mm high) lies in the parting plane toward -x in a closed 12 x 10 pocket; the 6 x 6 cable notch is in the middle of the opposite (+x) wall, 3 mm in each half, 9.7..15.7 mm above the plate top. Beam apertures in the covers are not yet machined.</t>
         </is>
       </c>
     </row>

--- a/Production/LatticeBoardV9/Lattice_Board_V9.xlsx
+++ b/Production/LatticeBoardV9/Lattice_Board_V9.xlsx
@@ -1,131 +1,130 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
-  <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-  </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
-</workbook>
+<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheets>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R17ea18d8122c4239"/>
+  </x:sheets>
+  <x:definedNames/>
+</x:workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
-    </font>
-  </fonts>
-  <fills count="2">
-    <fill>
-      <patternFill/>
-    </fill>
-    <fill>
-      <patternFill patternType="gray125"/>
-    </fill>
-  </fills>
-  <borders count="1">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-  </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-  </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-  </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
-  </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
-</styleSheet>
+<x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:fonts count="2">
+    <x:font>
+      <x:sz val="11"/>
+      <x:color theme="1"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+      <x:scheme val="minor"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+    </x:font>
+  </x:fonts>
+  <x:fills count="2">
+    <x:fill>
+      <x:patternFill patternType="none"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="gray125"/>
+    </x:fill>
+  </x:fills>
+  <x:borders count="1">
+    <x:border>
+      <x:left/>
+      <x:right/>
+      <x:top/>
+      <x:bottom/>
+      <x:diagonal/>
+    </x:border>
+  </x:borders>
+  <x:cellStyleXfs count="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </x:cellStyleXfs>
+  <x:cellXfs count="3">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+  </x:cellXfs>
+  <x:cellStyles count="1">
+    <x:cellStyle name="Normal" xfId="0"/>
+  </x:cellStyles>
+  <x:colors>
+    <x:indexedColors>
+      <x:rgbColor rgb="00000000"/>
+      <x:rgbColor rgb="00FFFFFF"/>
+      <x:rgbColor rgb="00FF0000"/>
+      <x:rgbColor rgb="0000FF00"/>
+      <x:rgbColor rgb="000000FF"/>
+      <x:rgbColor rgb="00FFFF00"/>
+      <x:rgbColor rgb="00FF00FF"/>
+      <x:rgbColor rgb="0000FFFF"/>
+      <x:rgbColor rgb="00000000"/>
+      <x:rgbColor rgb="00FFFFFF"/>
+      <x:rgbColor rgb="00FF0000"/>
+      <x:rgbColor rgb="0000FF00"/>
+      <x:rgbColor rgb="000000FF"/>
+      <x:rgbColor rgb="00FFFF00"/>
+      <x:rgbColor rgb="00FF00FF"/>
+      <x:rgbColor rgb="0000FFFF"/>
+      <x:rgbColor rgb="00800000"/>
+      <x:rgbColor rgb="00008000"/>
+      <x:rgbColor rgb="00000080"/>
+      <x:rgbColor rgb="00808000"/>
+      <x:rgbColor rgb="00800080"/>
+      <x:rgbColor rgb="00008080"/>
+      <x:rgbColor rgb="00C0C0C0"/>
+      <x:rgbColor rgb="00808080"/>
+      <x:rgbColor rgb="009999FF"/>
+      <x:rgbColor rgb="00993366"/>
+      <x:rgbColor rgb="00FFFFCC"/>
+      <x:rgbColor rgb="00CCFFFF"/>
+      <x:rgbColor rgb="00660066"/>
+      <x:rgbColor rgb="00FF8080"/>
+      <x:rgbColor rgb="000066CC"/>
+      <x:rgbColor rgb="00CCCCFF"/>
+      <x:rgbColor rgb="00000080"/>
+      <x:rgbColor rgb="00FF00FF"/>
+      <x:rgbColor rgb="00FFFF00"/>
+      <x:rgbColor rgb="0000FFFF"/>
+      <x:rgbColor rgb="00800080"/>
+      <x:rgbColor rgb="00800000"/>
+      <x:rgbColor rgb="00008080"/>
+      <x:rgbColor rgb="000000FF"/>
+      <x:rgbColor rgb="0000CCFF"/>
+      <x:rgbColor rgb="00CCFFFF"/>
+      <x:rgbColor rgb="00CCFFCC"/>
+      <x:rgbColor rgb="00FFFF99"/>
+      <x:rgbColor rgb="0099CCFF"/>
+      <x:rgbColor rgb="00FF99CC"/>
+      <x:rgbColor rgb="00CC99FF"/>
+      <x:rgbColor rgb="00FFCC99"/>
+      <x:rgbColor rgb="003366FF"/>
+      <x:rgbColor rgb="0033CCCC"/>
+      <x:rgbColor rgb="0099CC00"/>
+      <x:rgbColor rgb="00FFCC00"/>
+      <x:rgbColor rgb="00FF9900"/>
+      <x:rgbColor rgb="00FF6600"/>
+      <x:rgbColor rgb="00666699"/>
+      <x:rgbColor rgb="00969696"/>
+      <x:rgbColor rgb="00003366"/>
+      <x:rgbColor rgb="00339966"/>
+      <x:rgbColor rgb="00003300"/>
+      <x:rgbColor rgb="00333300"/>
+      <x:rgbColor rgb="00993300"/>
+      <x:rgbColor rgb="00993366"/>
+      <x:rgbColor rgb="00333399"/>
+      <x:rgbColor rgb="00333333"/>
+    </x:indexedColors>
+  </x:colors>
+</x:styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -292,7 +291,7 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
@@ -301,13 +300,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -341,17 +340,6 @@
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -406,8 +394,6 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -427,7 +413,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Lattice board V9.7 with cell enclosure V9.16 (24 x 15 in, f = 300 folded cat-eyes, sliding Rb cell enclosure of two identical half bodies, two end screws) - single-TA configuration + external-TA option</t>
+          <t xml:space="preserve">Lattice board V9.7 with cell enclosure V9.16 (24 x 15 in, f = 300 folded cat-eyes, sliding Rb cell enclosure of two identical half bodies, two end screws) - single-TA configuration + external-TA option</t>
         </is>
       </c>
     </row>
@@ -435,19 +421,19 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Adaptors</t>
+          <t xml:space="preserve">Adaptors</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>#</t>
+          <t xml:space="preserve">#</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AOM_Adapter.step (upper AOM adapter; the lower seat is machined into the baseplate)</t>
+          <t xml:space="preserve">AOM_Adapter.step (upper AOM adapter; the lower seat is machined into the baseplate)</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -457,7 +443,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cube_Mount_Halfinch.step</t>
+          <t xml:space="preserve">Cube_Mount_Halfinch.step</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -467,7 +453,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Iris_Mount.step (IDA12 slide mount)</t>
+          <t xml:space="preserve">Iris_Mount.step (IDA12 slide mount)</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -477,7 +463,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Rb_Cell_Enclosure_Cover_V9_16.step (Production/CellEnclosure; machined, 7 mm end cover, no aperture yet)</t>
+          <t xml:space="preserve">Rb_Cell_Enclosure_Cover_V9_16.step (Production/CellEnclosure; machined, 7 mm end cover, no aperture yet)</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -487,7 +473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Rb_Cell_Enclosure_HalfBody_V9_16.step (Production/CellEnclosure; machined half body 88 x 46.9 x 24, two plain through slots; lower and upper half are this same part)</t>
+          <t xml:space="preserve">Rb_Cell_Enclosure_HalfBody_V9_16.step (Production/CellEnclosure; machined half body 88 x 46.9 x 24, two plain through slots; lower and upper half are this same part)</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -497,7 +483,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Shutter_Adapter.step</t>
+          <t xml:space="preserve">Shutter_Adapter.step</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -507,7 +493,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Surface_Adapter_isolator_lip.step</t>
+          <t xml:space="preserve">Surface_Adapter_isolator_lip.step</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -517,7 +503,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Surface_Adapter_rsp05_lip.step</t>
+          <t xml:space="preserve">Surface_Adapter_rsp05_lip.step</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -527,7 +513,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TA_adapter.step</t>
+          <t xml:space="preserve">TA_adapter.step</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -537,7 +523,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>8-32 UNC x 5/8 in socket head cap screw (8 cover screws of the cell enclosure)</t>
+          <t xml:space="preserve">8-32 UNC x 5/8 in socket head cap screw (8 cover screws of the cell enclosure)</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -547,7 +533,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>8-32 UNC x 2-1/4 in socket head cap screw (through the slots of both enclosure halves into the plate, one per end)</t>
+          <t xml:space="preserve">8-32 UNC x 2-1/4 in socket head cap screw (through the slots of both enclosure halves into the plate, one per end)</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -557,7 +543,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>#8 flat washer (under the two 2-1/4 in screw heads, on the slots)</t>
+          <t xml:space="preserve">#8 flat washer (under the two 2-1/4 in screw heads, on the slots)</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -567,7 +553,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Lattice_V9_7_baseplate_24x15in.step</t>
+          <t xml:space="preserve">Lattice_V9_7_baseplate_24x15in.step</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -578,19 +564,19 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Elements</t>
+          <t xml:space="preserve">Elements</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>#</t>
+          <t xml:space="preserve">#</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1/2 in half-wave waveplate (HWP)</t>
+          <t xml:space="preserve">1/2 in half-wave waveplate (HWP)</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -600,7 +586,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1/2 in mirror (BB05-E03 or equivalent)</t>
+          <t xml:space="preserve">1/2 in mirror (BB05-E03 or equivalent)</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -610,7 +596,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1/2 in quarter-wave waveplate (QWP)</t>
+          <t xml:space="preserve">1/2 in quarter-wave waveplate (QWP)</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -620,7 +606,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1/4-20 table bolt (baseplate fixing)</t>
+          <t xml:space="preserve">1/4-20 table bolt (baseplate fixing)</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -630,7 +616,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>C220TMD-A fiber lens</t>
+          <t xml:space="preserve">C220TMD-A fiber lens</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -640,7 +626,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>G&amp;H AOMO 3100-125</t>
+          <t xml:space="preserve">G&amp;H AOMO 3100-125</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -650,7 +636,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>HKTS-5/64 thumbscrew adjuster</t>
+          <t xml:space="preserve">HKTS-5/64 thumbscrew adjuster</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -660,7 +646,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>IDA12-P5 iris</t>
+          <t xml:space="preserve">IDA12-P5 iris</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -670,7 +656,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>IOT-5-850-VLP isolator (113.5 mm plate pocket)</t>
+          <t xml:space="preserve">IOT-5-850-VLP isolator (113.5 mm plate pocket)</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -680,7 +666,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>KA05T fiber port mount (rear tail-clamp hole pair drilled in the plate: lattice 76 mm, TA / AOM boards 82.7 mm behind the head)</t>
+          <t xml:space="preserve">KA05T fiber port mount (rear tail-clamp hole pair drilled in the plate: lattice 76 mm, TA / AOM boards 82.7 mm behind the head)</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -690,7 +676,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>KM100PM (bridged)</t>
+          <t xml:space="preserve">KM100PM (bridged)</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -700,7 +686,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Lens LA1289-B</t>
+          <t xml:space="preserve">Lens LA1289-B</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -710,7 +696,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lens LA1540-B</t>
+          <t xml:space="preserve">Lens LA1540-B</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -720,7 +706,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Lens LA1618-B</t>
+          <t xml:space="preserve">Lens LA1618-B</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -730,7 +716,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Newport M05 mirror mount</t>
+          <t xml:space="preserve">Newport M05 mirror mount</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -740,7 +726,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>PBS cube 12.7 mm</t>
+          <t xml:space="preserve">PBS cube 12.7 mm</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -750,7 +736,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>POLARIS-L05G lens holder (no alignment-pin slots cut)</t>
+          <t xml:space="preserve">POLARIS-L05G lens holder (no alignment-pin slots cut)</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -760,7 +746,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>RSP05 rotation mount</t>
+          <t xml:space="preserve">RSP05 rotation mount</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -770,7 +756,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Rb vapour cell GC25075-RB (25.4 x 71.84 mm, fill stem sideways in the parting plane, toward board -x)</t>
+          <t xml:space="preserve">Rb vapour cell GC25075-RB (25.4 x 71.84 mm, fill stem sideways in the parting plane, toward board -x)</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -780,7 +766,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>S05TM09</t>
+          <t xml:space="preserve">S05TM09</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -790,7 +776,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SM05FCA2</t>
+          <t xml:space="preserve">SM05FCA2</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -800,7 +786,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SM05L05</t>
+          <t xml:space="preserve">SM05L05</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -810,7 +796,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SRS SR475 shutter</t>
+          <t xml:space="preserve">SRS SR475 shutter</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -820,7 +806,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>TA butterfly package (TAboard), mounted on the TA adapter</t>
+          <t xml:space="preserve">TA butterfly package (TAboard), mounted on the TA adapter</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -831,19 +817,19 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>External-TA option only (not installed in the single-TA configuration)</t>
+          <t xml:space="preserve">External-TA option only (not installed in the single-TA configuration)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>#</t>
+          <t xml:space="preserve">#</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Iris_Mount.step (IDA12 slide mount)</t>
+          <t xml:space="preserve">Iris_Mount.step (IDA12 slide mount)</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -853,7 +839,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1/2 in mirror (BB05-E03 or equivalent)</t>
+          <t xml:space="preserve">1/2 in mirror (BB05-E03 or equivalent)</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -863,7 +849,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>C220TMD-A fiber lens</t>
+          <t xml:space="preserve">C220TMD-A fiber lens</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -873,7 +859,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>HKTS-5/64 thumbscrew adjuster</t>
+          <t xml:space="preserve">HKTS-5/64 thumbscrew adjuster</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -883,7 +869,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>IDA12-P5 iris</t>
+          <t xml:space="preserve">IDA12-P5 iris</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -893,7 +879,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>KA05T fiber port mount (rear tail-clamp hole pair drilled in the plate: lattice 76 mm, TA / AOM boards 82.7 mm behind the head)</t>
+          <t xml:space="preserve">KA05T fiber port mount (rear tail-clamp hole pair drilled in the plate: lattice 76 mm, TA / AOM boards 82.7 mm behind the head)</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -903,7 +889,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Newport M05 mirror mount</t>
+          <t xml:space="preserve">Newport M05 mirror mount</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -913,7 +899,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>S05TM09</t>
+          <t xml:space="preserve">S05TM09</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -923,7 +909,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SM05FCA2</t>
+          <t xml:space="preserve">SM05FCA2</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -933,7 +919,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SM05L05</t>
+          <t xml:space="preserve">SM05L05</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -944,84 +930,83 @@
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t xml:space="preserve">Notes</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Which holes are tapped and which are not: see Lattice_V9_7_baseplate_TAP_or_NOT next to the STEP file (100 x 8-32 tapped, 4 x 1/4-20 table-bolt clearance); for the cell enclosure parts see Production/CellEnclosure/Rb_Cell_Enclosure_V9_16_3D_TAP.png.</t>
+          <t xml:space="preserve">Which holes are tapped and which are not: see Lattice_V9_7_baseplate_TAP_or_NOT next to the STEP file (100 x 8-32 tapped, 4 x 1/4-20 table-bolt clearance); for the cell enclosure parts see Production/CellEnclosure/Rb_Cell_Enclosure_V9_16_3D_TAP.png.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Counts come from the FreeCAD model (Lattice_V9_dual_validation.json); adapters are per hana-branch Production/Adapters STEP names.</t>
+          <t xml:space="preserve">Counts come from the FreeCAD model (Lattice_V9_dual_validation.json); adapters are per hana-branch Production/Adapters STEP names.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>The empty RSP05 mounts on the output rows receive a bonded PBS cube each (not modelled): add 1 cube per "empty rotating PBS RSP05".</t>
+          <t xml:space="preserve">The empty RSP05 mounts on the output rows receive a bonded PBS cube each (not modelled): add 1 cube per "empty rotating PBS RSP05".</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>HKTS-5/64 adjusters are the two per M05 / KA05T mount (already included with the mounts if bought as kits). Every mirror on this board is in a Newport M05.</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>AOM seats are machined into the baseplate (integral seat, flat screw face); only the upper AOM adapter is a separate part.</t>
-        </is>
-      </c>
+          <t xml:space="preserve">HKTS-5/64 adjusters are the two per M05 / KA05T mount (already included with the mounts if bought as kits). Every mirror on this board is in a Newport M05.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="88" customHeight="1">
+      <c r="A61" s="2" t="str">
+        <v>The 2 integral AOM seats have 6 mm side clearance and a 4 mm-deep front relief with R3 corners. Bearing faces and installation height are unchanged. Only the upper AOM adapter is a separate part. Single-axis pitch-down 0-4 degrees has a minimum floor gap of 1.06559 mm and sidewall gap of 3 mm. Combined-axis travel is not certified. Use the configuration-specific STEP/tapping sheet for f75-50 or f75-75; their original optional mounting recesses differ from f300.</v>
+      </c>
+      <c r="B61" s="2"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Cat-eye lens LA1618-B (f = 300 mm, 1/2 in): catalogue R 155.0 / tc 2.2 / te 2.1 mm. The plate was laid out with R 154.5 / tc 2.0; the resulting 1.2 / 1.0 mm cat-eye defocus is accepted (see the script docstring).</t>
+          <t xml:space="preserve">Cat-eye lens LA1618-B (f = 300 mm, 1/2 in): catalogue R 155.0 / tc 2.2 / te 2.1 mm. The plate was laid out with R 154.5 / tc 2.0; the resulting 1.2 / 1.0 mm cat-eye defocus is accepted (see the script docstring).</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>The TA butterfly board is screwed to the TA adapter (four M2.5 tapped in the adapter); the plate under the TA has only the adapter's four 8-32 taps, no M2.5 holes. Which holes are tapped: see the TAP_or_NOT sheet next to the STEP file.</t>
+          <t xml:space="preserve">The TA butterfly board is screwed to the TA adapter (four M2.5 tapped in the adapter); the plate under the TA has only the adapter's four 8-32 taps, no M2.5 holes. Which holes are tapped: see the TAP_or_NOT sheet next to the STEP file.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Table bolts (V9.4.2): the four 1/4-20 clearance holes sit on the lab table 1 in grid with the plate fiber-side (right) edge 0.25 in inside the table edge; both pairs 10 in apart and centred on the short edge - fiber-side pair 6.25 in from the right plate edge, TA-side pair 1.5 in from the left edge (16 in further left). STEP coordinates (mm): (447.675, 50.8), (447.675, 304.8), (41.275, 50.8), (41.275, 304.8).</t>
+          <t xml:space="preserve">Table bolts (V9.4.2): the four 1/4-20 clearance holes sit on the lab table 1 in grid with the plate fiber-side (right) edge 0.25 in inside the table edge; both pairs 10 in apart and centred on the short edge - fiber-side pair 6.25 in from the right plate edge, TA-side pair 1.5 in from the left edge (16 in further left). STEP coordinates (mm): (447.675, 50.8), (447.675, 304.8), (41.275, 50.8), (41.275, 304.8).</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>OPTIONAL f = 75 mm cat-eye (the V9.3 LA1612-B set) on the 0-order (input) axis straight after each AOM, bare holes only, nothing installed and nothing listed above: per AOM arm one L05G tap, two RSP05 taps, one slide-mount tap and two M05 taps (lens-&gt;mirror 50 and 75). To use it: 1 x LA1612-B in a POLARIS-L05G, 1 x RSP05 + lip adapter with a 1/2 in QWP, 1 x IDA12 on the slide mount, 1 x M05 retro mirror per arm. The M05 at those positions has no thumbscrew pocket: drive its lower adjuster with a plain 5/64 hex key (no HKTS). The lens-&gt;mirror 75 mirror body stands where fold F1 (DP1) / F3 (DP2) is, so that fold comes off for a 75/75 test.</t>
+          <t xml:space="preserve">OPTIONAL f = 75 mm cat-eye (the V9.3 LA1612-B set) on the 0-order (input) axis straight after each AOM, bare holes only, nothing installed and nothing listed above: per AOM arm one L05G tap, two RSP05 taps, one slide-mount tap and two M05 taps (lens-&gt;mirror 50 and 75). To use it: 1 x LA1612-B in a POLARIS-L05G, 1 x RSP05 + lip adapter with a 1/2 in QWP, 1 x IDA12 on the slide mount, 1 x M05 retro mirror per arm. The M05 at those positions has no thumbscrew pocket: drive its lower adjuster with a plain 5/64 hex key (no HKTS). The lens-&gt;mirror 75 mirror body stands where fold F1 (DP1) / F3 (DP2) is, so that fold comes off for a 75/75 test.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Six common stations are drilled as bare 8-32 holes; no holder or optic is installed. They are sized for a POLARIS-L05G with a 10 mm cylindrical lens bonded to its front face.</t>
+          <t xml:space="preserve">Six common stations are drilled as bare 8-32 holes; no holder or optic is installed. They are sized for a POLARIS-L05G with a 10 mm cylindrical lens bonded to its front face.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Cell enclosure V9.16 (the plate and its seat are unchanged since V9.7): the seat is an 11.3 mm deep pocket (104.4 x 64.7 mm, board x 157.8..222.5 / y 111.3..215.7) with two 8-32 taps through its floor at (185, 123.6) and (185, 203.4). The split plain-block enclosure is 2 identical half bodies (the upper one is the lower one turned over) + 2 identical end covers (Production/CellEnclosure). Two 8-32 x 2-1/4 in socket head cap screws with #8 flat washers, one per end, go from the top face through the plain through slots of both halves (in the bore end regions beyond the cell; no counter-slot, the heads sit on the top face) into the taps (9.2 mm of thread in the 14.1 mm pocket floor) and clamp the halves and the position; travel 10.5 mm toward -x (beam through the cell centre .. 2.2 mm inside the cell wall). The end covers (7 mm) are held by 8 x 8-32 x 5/8 in socket head cap screws (counterbored 3.5, 16 mm deep taps, two in each end face of each half) and tie the halves together. The fill stem (Thorlabs 24088-E0W: mid-length, &lt; 10 mm high) lies in the parting plane toward -x in a closed 12 x 10 pocket; the 6 x 6 cable notch is in the middle of the opposite (+x) wall, 3 mm in each half, 9.7..15.7 mm above the plate top. Beam apertures in the covers are not yet machined.</t>
+          <t xml:space="preserve">Cell enclosure V9.16 (the plate and its seat are unchanged since V9.7): the seat is an 11.3 mm deep pocket (104.4 x 64.7 mm, board x 157.8..222.5 / y 111.3..215.7) with two 8-32 taps through its floor at (185, 123.6) and (185, 203.4). The split plain-block enclosure is 2 identical half bodies (the upper one is the lower one turned over) + 2 identical end covers (Production/CellEnclosure). Two 8-32 x 2-1/4 in socket head cap screws with #8 flat washers, one per end, go from the top face through the plain through slots of both halves (in the bore end regions beyond the cell; no counter-slot, the heads sit on the top face) into the taps (9.2 mm of thread in the 14.1 mm pocket floor) and clamp the halves and the position; travel 10.5 mm toward -x (beam through the cell centre .. 2.2 mm inside the cell wall). The end covers (7 mm) are held by 8 x 8-32 x 5/8 in socket head cap screws (counterbored 3.5, 16 mm deep taps, two in each end face of each half) and tie the halves together. The fill stem (Thorlabs 24088-E0W: mid-length, &lt; 10 mm high) lies in the parting plane toward -x in a closed 12 x 10 pocket; the 6 x 6 cable notch is in the middle of the opposite (+x) wall, 3 mm in each half, 9.7..15.7 mm above the plate top. Beam apertures in the covers are not yet machined.</t>
         </is>
       </c>
     </row>
